--- a/artfynd/A 58368-2024 artfynd.xlsx
+++ b/artfynd/A 58368-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>123333781</v>
+        <v>123333788</v>
       </c>
       <c r="B2" t="n">
-        <v>57478</v>
+        <v>57481</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>515661</v>
+        <v>515844</v>
       </c>
       <c r="R2" t="n">
-        <v>7005038</v>
+        <v>7004872</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -782,10 +782,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123333793</v>
+        <v>123333782</v>
       </c>
       <c r="B3" t="n">
-        <v>79847</v>
+        <v>57481</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -798,21 +798,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -822,10 +822,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>515756</v>
+        <v>515629</v>
       </c>
       <c r="R3" t="n">
-        <v>7004969</v>
+        <v>7004991</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -858,6 +858,11 @@
       <c r="AA3" t="inlineStr">
         <is>
           <t>2025-03-20</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -884,10 +889,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123333794</v>
+        <v>123333791</v>
       </c>
       <c r="B4" t="n">
-        <v>79847</v>
+        <v>79850</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -924,10 +929,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>515718</v>
+        <v>515731</v>
       </c>
       <c r="R4" t="n">
-        <v>7004917</v>
+        <v>7004974</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -986,10 +991,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>123333782</v>
+        <v>123333793</v>
       </c>
       <c r="B5" t="n">
-        <v>57478</v>
+        <v>79850</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1002,21 +1007,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1026,10 +1031,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>515629</v>
+        <v>515756</v>
       </c>
       <c r="R5" t="n">
-        <v>7004991</v>
+        <v>7004969</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1062,11 +1067,6 @@
       <c r="AA5" t="inlineStr">
         <is>
           <t>2025-03-20</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1093,10 +1093,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>123333786</v>
+        <v>123333790</v>
       </c>
       <c r="B6" t="n">
-        <v>57478</v>
+        <v>79850</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1109,21 +1109,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1133,10 +1133,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>515911</v>
+        <v>515654</v>
       </c>
       <c r="R6" t="n">
-        <v>7004907</v>
+        <v>7005065</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1169,11 +1169,6 @@
       <c r="AA6" t="inlineStr">
         <is>
           <t>2025-03-20</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1200,10 +1195,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>123333791</v>
+        <v>123333779</v>
       </c>
       <c r="B7" t="n">
-        <v>79847</v>
+        <v>57481</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1216,21 +1211,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1240,10 +1235,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>515731</v>
+        <v>515628</v>
       </c>
       <c r="R7" t="n">
-        <v>7004974</v>
+        <v>7004943</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1276,6 +1271,11 @@
       <c r="AA7" t="inlineStr">
         <is>
           <t>2025-03-20</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1302,10 +1302,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>123333783</v>
+        <v>123333795</v>
       </c>
       <c r="B8" t="n">
-        <v>57478</v>
+        <v>56683</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1318,16 +1318,16 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100109</v>
+        <v>102612</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -1335,17 +1335,25 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I8" t="inlineStr"/>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr"/>
+      <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
           <t>Näverbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>515764</v>
+        <v>515669</v>
       </c>
       <c r="R8" t="n">
-        <v>7004977</v>
+        <v>7005043</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1382,7 +1390,7 @@
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>minst 2 hörda</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1409,10 +1417,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>123333784</v>
+        <v>123333783</v>
       </c>
       <c r="B9" t="n">
-        <v>57478</v>
+        <v>57481</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1449,10 +1457,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>515758</v>
+        <v>515764</v>
       </c>
       <c r="R9" t="n">
-        <v>7004972</v>
+        <v>7004977</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1489,7 +1497,7 @@
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1516,10 +1524,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>123333789</v>
+        <v>123333781</v>
       </c>
       <c r="B10" t="n">
-        <v>57478</v>
+        <v>57481</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1556,10 +1564,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>515716</v>
+        <v>515661</v>
       </c>
       <c r="R10" t="n">
-        <v>7004917</v>
+        <v>7005038</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1623,10 +1631,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>123333785</v>
+        <v>123333784</v>
       </c>
       <c r="B11" t="n">
-        <v>57478</v>
+        <v>57481</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1663,10 +1671,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>515764</v>
+        <v>515758</v>
       </c>
       <c r="R11" t="n">
-        <v>7004967</v>
+        <v>7004972</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1703,7 +1711,7 @@
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1730,10 +1738,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>123333795</v>
+        <v>123333789</v>
       </c>
       <c r="B12" t="n">
-        <v>56680</v>
+        <v>57481</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1746,16 +1754,16 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>102612</v>
+        <v>100109</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -1763,25 +1771,17 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K12" t="inlineStr"/>
-      <c r="L12" t="inlineStr"/>
-      <c r="M12" t="inlineStr"/>
-      <c r="N12" t="inlineStr"/>
+      <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
           <t>Näverbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>515669</v>
+        <v>515716</v>
       </c>
       <c r="R12" t="n">
-        <v>7005043</v>
+        <v>7004917</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1818,7 +1818,7 @@
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>minst 2 hörda</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1845,10 +1845,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>123333792</v>
+        <v>123333786</v>
       </c>
       <c r="B13" t="n">
-        <v>79847</v>
+        <v>57481</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1861,21 +1861,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1885,10 +1885,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>515741</v>
+        <v>515911</v>
       </c>
       <c r="R13" t="n">
-        <v>7004964</v>
+        <v>7004907</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1921,6 +1921,11 @@
       <c r="AA13" t="inlineStr">
         <is>
           <t>2025-03-20</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1947,10 +1952,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>123333790</v>
+        <v>123333792</v>
       </c>
       <c r="B14" t="n">
-        <v>79847</v>
+        <v>79850</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1987,10 +1992,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>515654</v>
+        <v>515741</v>
       </c>
       <c r="R14" t="n">
-        <v>7005065</v>
+        <v>7004964</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2049,10 +2054,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>123333779</v>
+        <v>123333794</v>
       </c>
       <c r="B15" t="n">
-        <v>57478</v>
+        <v>79850</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2065,21 +2070,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2089,10 +2094,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>515628</v>
+        <v>515718</v>
       </c>
       <c r="R15" t="n">
-        <v>7004943</v>
+        <v>7004917</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2125,11 +2130,6 @@
       <c r="AA15" t="inlineStr">
         <is>
           <t>2025-03-20</t>
-        </is>
-      </c>
-      <c r="AC15" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2156,10 +2156,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>123333787</v>
+        <v>123333785</v>
       </c>
       <c r="B16" t="n">
-        <v>57478</v>
+        <v>57481</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2196,10 +2196,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>515914</v>
+        <v>515764</v>
       </c>
       <c r="R16" t="n">
-        <v>7004901</v>
+        <v>7004967</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2263,10 +2263,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>123333788</v>
+        <v>123333787</v>
       </c>
       <c r="B17" t="n">
-        <v>57478</v>
+        <v>57481</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2303,10 +2303,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>515844</v>
+        <v>515914</v>
       </c>
       <c r="R17" t="n">
-        <v>7004872</v>
+        <v>7004901</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>

--- a/artfynd/A 58368-2024 artfynd.xlsx
+++ b/artfynd/A 58368-2024 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>123333788</v>
+        <v>123333782</v>
       </c>
       <c r="B2" t="n">
         <v>57481</v>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>515844</v>
+        <v>515629</v>
       </c>
       <c r="R2" t="n">
-        <v>7004872</v>
+        <v>7004991</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -755,7 +755,7 @@
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -782,7 +782,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123333782</v>
+        <v>123333779</v>
       </c>
       <c r="B3" t="n">
         <v>57481</v>
@@ -822,10 +822,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>515629</v>
+        <v>515628</v>
       </c>
       <c r="R3" t="n">
-        <v>7004991</v>
+        <v>7004943</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -862,7 +862,7 @@
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -892,7 +892,7 @@
         <v>123333791</v>
       </c>
       <c r="B4" t="n">
-        <v>79850</v>
+        <v>79852</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -991,10 +991,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>123333793</v>
+        <v>123333784</v>
       </c>
       <c r="B5" t="n">
-        <v>79850</v>
+        <v>57481</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1007,21 +1007,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1031,10 +1031,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>515756</v>
+        <v>515758</v>
       </c>
       <c r="R5" t="n">
-        <v>7004969</v>
+        <v>7004972</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1067,6 +1067,11 @@
       <c r="AA5" t="inlineStr">
         <is>
           <t>2025-03-20</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1093,10 +1098,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>123333790</v>
+        <v>123333788</v>
       </c>
       <c r="B6" t="n">
-        <v>79850</v>
+        <v>57481</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1109,21 +1114,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1133,10 +1138,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>515654</v>
+        <v>515844</v>
       </c>
       <c r="R6" t="n">
-        <v>7005065</v>
+        <v>7004872</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1169,6 +1174,11 @@
       <c r="AA6" t="inlineStr">
         <is>
           <t>2025-03-20</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1195,7 +1205,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>123333779</v>
+        <v>123333789</v>
       </c>
       <c r="B7" t="n">
         <v>57481</v>
@@ -1235,10 +1245,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>515628</v>
+        <v>515716</v>
       </c>
       <c r="R7" t="n">
-        <v>7004943</v>
+        <v>7004917</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1302,10 +1312,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>123333795</v>
+        <v>123333783</v>
       </c>
       <c r="B8" t="n">
-        <v>56683</v>
+        <v>57481</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1318,16 +1328,16 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>102612</v>
+        <v>100109</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -1335,25 +1345,17 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K8" t="inlineStr"/>
-      <c r="L8" t="inlineStr"/>
-      <c r="M8" t="inlineStr"/>
-      <c r="N8" t="inlineStr"/>
+      <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
           <t>Näverbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>515669</v>
+        <v>515764</v>
       </c>
       <c r="R8" t="n">
-        <v>7005043</v>
+        <v>7004977</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1390,7 +1392,7 @@
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>minst 2 hörda</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1417,7 +1419,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>123333783</v>
+        <v>123333787</v>
       </c>
       <c r="B9" t="n">
         <v>57481</v>
@@ -1457,10 +1459,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>515764</v>
+        <v>515914</v>
       </c>
       <c r="R9" t="n">
-        <v>7004977</v>
+        <v>7004901</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1524,10 +1526,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>123333781</v>
+        <v>123333795</v>
       </c>
       <c r="B10" t="n">
-        <v>57481</v>
+        <v>56683</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1540,16 +1542,16 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100109</v>
+        <v>102612</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -1557,17 +1559,25 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I10" t="inlineStr"/>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
+      <c r="M10" t="inlineStr"/>
+      <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
           <t>Näverbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>515661</v>
+        <v>515669</v>
       </c>
       <c r="R10" t="n">
-        <v>7005038</v>
+        <v>7005043</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1604,7 +1614,7 @@
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>minst 2 hörda</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1631,10 +1641,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>123333784</v>
+        <v>123333793</v>
       </c>
       <c r="B11" t="n">
-        <v>57481</v>
+        <v>79852</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1647,21 +1657,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1671,10 +1681,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>515758</v>
+        <v>515756</v>
       </c>
       <c r="R11" t="n">
-        <v>7004972</v>
+        <v>7004969</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1707,11 +1717,6 @@
       <c r="AA11" t="inlineStr">
         <is>
           <t>2025-03-20</t>
-        </is>
-      </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1738,10 +1743,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>123333789</v>
+        <v>123333790</v>
       </c>
       <c r="B12" t="n">
-        <v>57481</v>
+        <v>79852</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1754,21 +1759,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1778,10 +1783,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>515716</v>
+        <v>515654</v>
       </c>
       <c r="R12" t="n">
-        <v>7004917</v>
+        <v>7005065</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1814,11 +1819,6 @@
       <c r="AA12" t="inlineStr">
         <is>
           <t>2025-03-20</t>
-        </is>
-      </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1952,10 +1952,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>123333792</v>
+        <v>123333794</v>
       </c>
       <c r="B14" t="n">
-        <v>79850</v>
+        <v>79852</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1992,10 +1992,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>515741</v>
+        <v>515718</v>
       </c>
       <c r="R14" t="n">
-        <v>7004964</v>
+        <v>7004917</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2054,10 +2054,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>123333794</v>
+        <v>123333785</v>
       </c>
       <c r="B15" t="n">
-        <v>79850</v>
+        <v>57481</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2070,21 +2070,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2094,10 +2094,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>515718</v>
+        <v>515764</v>
       </c>
       <c r="R15" t="n">
-        <v>7004917</v>
+        <v>7004967</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2130,6 +2130,11 @@
       <c r="AA15" t="inlineStr">
         <is>
           <t>2025-03-20</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2156,10 +2161,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>123333785</v>
+        <v>123333792</v>
       </c>
       <c r="B16" t="n">
-        <v>57481</v>
+        <v>79852</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2172,21 +2177,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2196,10 +2201,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>515764</v>
+        <v>515741</v>
       </c>
       <c r="R16" t="n">
-        <v>7004967</v>
+        <v>7004964</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2232,11 +2237,6 @@
       <c r="AA16" t="inlineStr">
         <is>
           <t>2025-03-20</t>
-        </is>
-      </c>
-      <c r="AC16" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2263,7 +2263,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>123333787</v>
+        <v>123333781</v>
       </c>
       <c r="B17" t="n">
         <v>57481</v>
@@ -2303,10 +2303,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>515914</v>
+        <v>515661</v>
       </c>
       <c r="R17" t="n">
-        <v>7004901</v>
+        <v>7005038</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>

--- a/artfynd/A 58368-2024 artfynd.xlsx
+++ b/artfynd/A 58368-2024 artfynd.xlsx
@@ -1845,10 +1845,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>123333786</v>
+        <v>123333794</v>
       </c>
       <c r="B13" t="n">
-        <v>57481</v>
+        <v>79852</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1861,21 +1861,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1885,10 +1885,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>515911</v>
+        <v>515718</v>
       </c>
       <c r="R13" t="n">
-        <v>7004907</v>
+        <v>7004917</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1921,11 +1921,6 @@
       <c r="AA13" t="inlineStr">
         <is>
           <t>2025-03-20</t>
-        </is>
-      </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1952,10 +1947,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>123333794</v>
+        <v>123333786</v>
       </c>
       <c r="B14" t="n">
-        <v>79852</v>
+        <v>57481</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1968,21 +1963,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1992,10 +1987,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>515718</v>
+        <v>515911</v>
       </c>
       <c r="R14" t="n">
-        <v>7004917</v>
+        <v>7004907</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2028,6 +2023,11 @@
       <c r="AA14" t="inlineStr">
         <is>
           <t>2025-03-20</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD14" t="b">

--- a/artfynd/A 58368-2024 artfynd.xlsx
+++ b/artfynd/A 58368-2024 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>123333782</v>
+        <v>123333785</v>
       </c>
       <c r="B2" t="n">
         <v>57481</v>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>515629</v>
+        <v>515764</v>
       </c>
       <c r="R2" t="n">
-        <v>7004991</v>
+        <v>7004967</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -755,7 +755,7 @@
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -782,7 +782,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123333779</v>
+        <v>123333783</v>
       </c>
       <c r="B3" t="n">
         <v>57481</v>
@@ -822,10 +822,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>515628</v>
+        <v>515764</v>
       </c>
       <c r="R3" t="n">
-        <v>7004943</v>
+        <v>7004977</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -889,10 +889,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123333791</v>
+        <v>123333784</v>
       </c>
       <c r="B4" t="n">
-        <v>79852</v>
+        <v>57481</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -905,21 +905,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -929,10 +929,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>515731</v>
+        <v>515758</v>
       </c>
       <c r="R4" t="n">
-        <v>7004974</v>
+        <v>7004972</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -965,6 +965,11 @@
       <c r="AA4" t="inlineStr">
         <is>
           <t>2025-03-20</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -991,7 +996,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>123333784</v>
+        <v>123333782</v>
       </c>
       <c r="B5" t="n">
         <v>57481</v>
@@ -1031,10 +1036,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>515758</v>
+        <v>515629</v>
       </c>
       <c r="R5" t="n">
-        <v>7004972</v>
+        <v>7004991</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1098,10 +1103,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>123333788</v>
+        <v>123333790</v>
       </c>
       <c r="B6" t="n">
-        <v>57481</v>
+        <v>79853</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1114,21 +1119,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1138,10 +1143,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>515844</v>
+        <v>515654</v>
       </c>
       <c r="R6" t="n">
-        <v>7004872</v>
+        <v>7005065</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1174,11 +1179,6 @@
       <c r="AA6" t="inlineStr">
         <is>
           <t>2025-03-20</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1205,7 +1205,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>123333789</v>
+        <v>123333787</v>
       </c>
       <c r="B7" t="n">
         <v>57481</v>
@@ -1245,10 +1245,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>515716</v>
+        <v>515914</v>
       </c>
       <c r="R7" t="n">
-        <v>7004917</v>
+        <v>7004901</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1312,10 +1312,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>123333783</v>
+        <v>123333795</v>
       </c>
       <c r="B8" t="n">
-        <v>57481</v>
+        <v>56683</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1328,16 +1328,16 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100109</v>
+        <v>102612</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -1345,17 +1345,25 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I8" t="inlineStr"/>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr"/>
+      <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
           <t>Näverbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>515764</v>
+        <v>515669</v>
       </c>
       <c r="R8" t="n">
-        <v>7004977</v>
+        <v>7005043</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1392,7 +1400,7 @@
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>minst 2 hörda</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1419,10 +1427,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>123333787</v>
+        <v>123333794</v>
       </c>
       <c r="B9" t="n">
-        <v>57481</v>
+        <v>79853</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1435,21 +1443,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1459,10 +1467,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>515914</v>
+        <v>515718</v>
       </c>
       <c r="R9" t="n">
-        <v>7004901</v>
+        <v>7004917</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1495,11 +1503,6 @@
       <c r="AA9" t="inlineStr">
         <is>
           <t>2025-03-20</t>
-        </is>
-      </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1526,10 +1529,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>123333795</v>
+        <v>123333779</v>
       </c>
       <c r="B10" t="n">
-        <v>56683</v>
+        <v>57481</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1542,16 +1545,16 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>102612</v>
+        <v>100109</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -1559,25 +1562,17 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K10" t="inlineStr"/>
-      <c r="L10" t="inlineStr"/>
-      <c r="M10" t="inlineStr"/>
-      <c r="N10" t="inlineStr"/>
+      <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
           <t>Näverbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>515669</v>
+        <v>515628</v>
       </c>
       <c r="R10" t="n">
-        <v>7005043</v>
+        <v>7004943</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1614,7 +1609,7 @@
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>minst 2 hörda</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1641,10 +1636,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>123333793</v>
+        <v>123333781</v>
       </c>
       <c r="B11" t="n">
-        <v>79852</v>
+        <v>57481</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1657,21 +1652,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1681,10 +1676,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>515756</v>
+        <v>515661</v>
       </c>
       <c r="R11" t="n">
-        <v>7004969</v>
+        <v>7005038</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1717,6 +1712,11 @@
       <c r="AA11" t="inlineStr">
         <is>
           <t>2025-03-20</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1743,10 +1743,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>123333790</v>
+        <v>123333789</v>
       </c>
       <c r="B12" t="n">
-        <v>79852</v>
+        <v>57481</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1759,21 +1759,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1783,10 +1783,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>515654</v>
+        <v>515716</v>
       </c>
       <c r="R12" t="n">
-        <v>7005065</v>
+        <v>7004917</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1819,6 +1819,11 @@
       <c r="AA12" t="inlineStr">
         <is>
           <t>2025-03-20</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1845,10 +1850,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>123333794</v>
+        <v>123333788</v>
       </c>
       <c r="B13" t="n">
-        <v>79852</v>
+        <v>57481</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1861,21 +1866,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1885,10 +1890,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>515718</v>
+        <v>515844</v>
       </c>
       <c r="R13" t="n">
-        <v>7004917</v>
+        <v>7004872</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1921,6 +1926,11 @@
       <c r="AA13" t="inlineStr">
         <is>
           <t>2025-03-20</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1947,10 +1957,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>123333786</v>
+        <v>123333791</v>
       </c>
       <c r="B14" t="n">
-        <v>57481</v>
+        <v>79853</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1963,21 +1973,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1987,10 +1997,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>515911</v>
+        <v>515731</v>
       </c>
       <c r="R14" t="n">
-        <v>7004907</v>
+        <v>7004974</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2023,11 +2033,6 @@
       <c r="AA14" t="inlineStr">
         <is>
           <t>2025-03-20</t>
-        </is>
-      </c>
-      <c r="AC14" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2054,10 +2059,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>123333785</v>
+        <v>123333792</v>
       </c>
       <c r="B15" t="n">
-        <v>57481</v>
+        <v>79853</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2070,21 +2075,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2094,10 +2099,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>515764</v>
+        <v>515741</v>
       </c>
       <c r="R15" t="n">
-        <v>7004967</v>
+        <v>7004964</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2130,11 +2135,6 @@
       <c r="AA15" t="inlineStr">
         <is>
           <t>2025-03-20</t>
-        </is>
-      </c>
-      <c r="AC15" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2161,10 +2161,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>123333792</v>
+        <v>123333793</v>
       </c>
       <c r="B16" t="n">
-        <v>79852</v>
+        <v>79853</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2201,10 +2201,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>515741</v>
+        <v>515756</v>
       </c>
       <c r="R16" t="n">
-        <v>7004964</v>
+        <v>7004969</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2263,7 +2263,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>123333781</v>
+        <v>123333786</v>
       </c>
       <c r="B17" t="n">
         <v>57481</v>
@@ -2303,10 +2303,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>515661</v>
+        <v>515911</v>
       </c>
       <c r="R17" t="n">
-        <v>7005038</v>
+        <v>7004907</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>

--- a/artfynd/A 58368-2024 artfynd.xlsx
+++ b/artfynd/A 58368-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>123333783</v>
+        <v>123333792</v>
       </c>
       <c r="B2" t="n">
-        <v>57481</v>
+        <v>79862</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>515764</v>
+        <v>515741</v>
       </c>
       <c r="R2" t="n">
-        <v>7004977</v>
+        <v>7004964</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -751,11 +751,6 @@
       <c r="AA2" t="inlineStr">
         <is>
           <t>2025-03-20</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -782,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123333787</v>
+        <v>123333786</v>
       </c>
       <c r="B3" t="n">
-        <v>57481</v>
+        <v>57487</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -822,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>515914</v>
+        <v>515911</v>
       </c>
       <c r="R3" t="n">
-        <v>7004901</v>
+        <v>7004907</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -889,10 +884,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123333785</v>
+        <v>123333790</v>
       </c>
       <c r="B4" t="n">
-        <v>57481</v>
+        <v>79862</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -905,21 +900,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -929,10 +924,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>515764</v>
+        <v>515654</v>
       </c>
       <c r="R4" t="n">
-        <v>7004967</v>
+        <v>7005065</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -965,11 +960,6 @@
       <c r="AA4" t="inlineStr">
         <is>
           <t>2025-03-20</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -996,10 +986,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>123333795</v>
+        <v>123333788</v>
       </c>
       <c r="B5" t="n">
-        <v>56683</v>
+        <v>57487</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1012,16 +1002,16 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>102612</v>
+        <v>100109</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -1029,25 +1019,17 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
-      <c r="M5" t="inlineStr"/>
-      <c r="N5" t="inlineStr"/>
+      <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
           <t>Näverbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>515669</v>
+        <v>515844</v>
       </c>
       <c r="R5" t="n">
-        <v>7005043</v>
+        <v>7004872</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1084,7 +1066,7 @@
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>minst 2 hörda</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1111,10 +1093,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>123333784</v>
+        <v>123333789</v>
       </c>
       <c r="B6" t="n">
-        <v>57481</v>
+        <v>57487</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1151,10 +1133,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>515758</v>
+        <v>515716</v>
       </c>
       <c r="R6" t="n">
-        <v>7004972</v>
+        <v>7004917</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1191,7 +1173,7 @@
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1218,10 +1200,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>123333794</v>
+        <v>123333793</v>
       </c>
       <c r="B7" t="n">
-        <v>79856</v>
+        <v>79862</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1258,10 +1240,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>515718</v>
+        <v>515756</v>
       </c>
       <c r="R7" t="n">
-        <v>7004917</v>
+        <v>7004969</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1320,10 +1302,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>123333788</v>
+        <v>123333787</v>
       </c>
       <c r="B8" t="n">
-        <v>57481</v>
+        <v>57487</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1360,10 +1342,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>515844</v>
+        <v>515914</v>
       </c>
       <c r="R8" t="n">
-        <v>7004872</v>
+        <v>7004901</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1427,10 +1409,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>123333779</v>
+        <v>123333785</v>
       </c>
       <c r="B9" t="n">
-        <v>57481</v>
+        <v>57487</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1467,10 +1449,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>515628</v>
+        <v>515764</v>
       </c>
       <c r="R9" t="n">
-        <v>7004943</v>
+        <v>7004967</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1537,7 +1519,7 @@
         <v>123333791</v>
       </c>
       <c r="B10" t="n">
-        <v>79856</v>
+        <v>79862</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1636,10 +1618,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>123333781</v>
+        <v>123333779</v>
       </c>
       <c r="B11" t="n">
-        <v>57481</v>
+        <v>57487</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1676,10 +1658,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>515661</v>
+        <v>515628</v>
       </c>
       <c r="R11" t="n">
-        <v>7005038</v>
+        <v>7004943</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1743,10 +1725,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>123333792</v>
+        <v>123333795</v>
       </c>
       <c r="B12" t="n">
-        <v>79856</v>
+        <v>56689</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1759,34 +1741,42 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6458</v>
+        <v>102612</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr"/>
+      <c r="M12" t="inlineStr"/>
+      <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
           <t>Näverbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>515741</v>
+        <v>515669</v>
       </c>
       <c r="R12" t="n">
-        <v>7004964</v>
+        <v>7005043</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1819,6 +1809,11 @@
       <c r="AA12" t="inlineStr">
         <is>
           <t>2025-03-20</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>minst 2 hörda</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1845,10 +1840,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>123333786</v>
+        <v>123333782</v>
       </c>
       <c r="B13" t="n">
-        <v>57481</v>
+        <v>57487</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1885,10 +1880,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>515911</v>
+        <v>515629</v>
       </c>
       <c r="R13" t="n">
-        <v>7004907</v>
+        <v>7004991</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1925,7 +1920,7 @@
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1952,10 +1947,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>123333789</v>
+        <v>123333783</v>
       </c>
       <c r="B14" t="n">
-        <v>57481</v>
+        <v>57487</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1992,10 +1987,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>515716</v>
+        <v>515764</v>
       </c>
       <c r="R14" t="n">
-        <v>7004917</v>
+        <v>7004977</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2059,10 +2054,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>123333793</v>
+        <v>123333794</v>
       </c>
       <c r="B15" t="n">
-        <v>79856</v>
+        <v>79862</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2099,10 +2094,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>515756</v>
+        <v>515718</v>
       </c>
       <c r="R15" t="n">
-        <v>7004969</v>
+        <v>7004917</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2161,10 +2156,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>123333782</v>
+        <v>123333784</v>
       </c>
       <c r="B16" t="n">
-        <v>57481</v>
+        <v>57487</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2201,10 +2196,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>515629</v>
+        <v>515758</v>
       </c>
       <c r="R16" t="n">
-        <v>7004991</v>
+        <v>7004972</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2268,10 +2263,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>123333790</v>
+        <v>123333781</v>
       </c>
       <c r="B17" t="n">
-        <v>79856</v>
+        <v>57487</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2284,21 +2279,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2308,10 +2303,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>515654</v>
+        <v>515661</v>
       </c>
       <c r="R17" t="n">
-        <v>7005065</v>
+        <v>7005038</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2344,6 +2339,11 @@
       <c r="AA17" t="inlineStr">
         <is>
           <t>2025-03-20</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD17" t="b">

--- a/artfynd/A 58368-2024 artfynd.xlsx
+++ b/artfynd/A 58368-2024 artfynd.xlsx
@@ -1725,10 +1725,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>123333795</v>
+        <v>123333782</v>
       </c>
       <c r="B12" t="n">
-        <v>56689</v>
+        <v>57487</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1741,16 +1741,16 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>102612</v>
+        <v>100109</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -1758,25 +1758,17 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K12" t="inlineStr"/>
-      <c r="L12" t="inlineStr"/>
-      <c r="M12" t="inlineStr"/>
-      <c r="N12" t="inlineStr"/>
+      <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
           <t>Näverbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>515669</v>
+        <v>515629</v>
       </c>
       <c r="R12" t="n">
-        <v>7005043</v>
+        <v>7004991</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1813,7 +1805,7 @@
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>minst 2 hörda</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1840,10 +1832,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>123333782</v>
+        <v>123333795</v>
       </c>
       <c r="B13" t="n">
-        <v>57487</v>
+        <v>56689</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1856,16 +1848,16 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100109</v>
+        <v>102612</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -1873,17 +1865,25 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I13" t="inlineStr"/>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr"/>
+      <c r="M13" t="inlineStr"/>
+      <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
           <t>Näverbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>515629</v>
+        <v>515669</v>
       </c>
       <c r="R13" t="n">
-        <v>7004991</v>
+        <v>7005043</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1920,7 +1920,7 @@
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>minst 2 hörda</t>
         </is>
       </c>
       <c r="AD13" t="b">

--- a/artfynd/A 58368-2024 artfynd.xlsx
+++ b/artfynd/A 58368-2024 artfynd.xlsx
@@ -1725,10 +1725,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>123333782</v>
+        <v>123333795</v>
       </c>
       <c r="B12" t="n">
-        <v>57487</v>
+        <v>56689</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1741,16 +1741,16 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100109</v>
+        <v>102612</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -1758,17 +1758,25 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I12" t="inlineStr"/>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr"/>
+      <c r="M12" t="inlineStr"/>
+      <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
           <t>Näverbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>515629</v>
+        <v>515669</v>
       </c>
       <c r="R12" t="n">
-        <v>7004991</v>
+        <v>7005043</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1805,7 +1813,7 @@
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>minst 2 hörda</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1832,10 +1840,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>123333795</v>
+        <v>123333782</v>
       </c>
       <c r="B13" t="n">
-        <v>56689</v>
+        <v>57487</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1848,16 +1856,16 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>102612</v>
+        <v>100109</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -1865,25 +1873,17 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K13" t="inlineStr"/>
-      <c r="L13" t="inlineStr"/>
-      <c r="M13" t="inlineStr"/>
-      <c r="N13" t="inlineStr"/>
+      <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
           <t>Näverbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>515669</v>
+        <v>515629</v>
       </c>
       <c r="R13" t="n">
-        <v>7005043</v>
+        <v>7004991</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1920,7 +1920,7 @@
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>minst 2 hörda</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD13" t="b">

--- a/artfynd/A 58368-2024 artfynd.xlsx
+++ b/artfynd/A 58368-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>123333792</v>
+        <v>123333784</v>
       </c>
       <c r="B2" t="n">
-        <v>79862</v>
+        <v>57490</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>515741</v>
+        <v>515758</v>
       </c>
       <c r="R2" t="n">
-        <v>7004964</v>
+        <v>7004972</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -751,6 +751,11 @@
       <c r="AA2" t="inlineStr">
         <is>
           <t>2025-03-20</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -777,10 +782,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123333786</v>
+        <v>123333795</v>
       </c>
       <c r="B3" t="n">
-        <v>57487</v>
+        <v>56692</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -793,16 +798,16 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100109</v>
+        <v>102612</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -810,17 +815,25 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I3" t="inlineStr"/>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr"/>
+      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
           <t>Näverbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>515911</v>
+        <v>515669</v>
       </c>
       <c r="R3" t="n">
-        <v>7004907</v>
+        <v>7005043</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -857,7 +870,7 @@
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>minst 2 hörda</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -884,10 +897,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123333790</v>
+        <v>123333792</v>
       </c>
       <c r="B4" t="n">
-        <v>79862</v>
+        <v>79867</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -924,10 +937,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>515654</v>
+        <v>515741</v>
       </c>
       <c r="R4" t="n">
-        <v>7005065</v>
+        <v>7004964</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -986,10 +999,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>123333788</v>
+        <v>123333783</v>
       </c>
       <c r="B5" t="n">
-        <v>57487</v>
+        <v>57490</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1026,10 +1039,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>515844</v>
+        <v>515764</v>
       </c>
       <c r="R5" t="n">
-        <v>7004872</v>
+        <v>7004977</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1093,10 +1106,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>123333789</v>
+        <v>123333779</v>
       </c>
       <c r="B6" t="n">
-        <v>57487</v>
+        <v>57490</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1133,10 +1146,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>515716</v>
+        <v>515628</v>
       </c>
       <c r="R6" t="n">
-        <v>7004917</v>
+        <v>7004943</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1200,10 +1213,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>123333793</v>
+        <v>123333787</v>
       </c>
       <c r="B7" t="n">
-        <v>79862</v>
+        <v>57490</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1216,21 +1229,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1240,10 +1253,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>515756</v>
+        <v>515914</v>
       </c>
       <c r="R7" t="n">
-        <v>7004969</v>
+        <v>7004901</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1276,6 +1289,11 @@
       <c r="AA7" t="inlineStr">
         <is>
           <t>2025-03-20</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1302,10 +1320,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>123333787</v>
+        <v>123333786</v>
       </c>
       <c r="B8" t="n">
-        <v>57487</v>
+        <v>57490</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1342,10 +1360,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>515914</v>
+        <v>515911</v>
       </c>
       <c r="R8" t="n">
-        <v>7004901</v>
+        <v>7004907</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1409,10 +1427,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>123333785</v>
+        <v>123333791</v>
       </c>
       <c r="B9" t="n">
-        <v>57487</v>
+        <v>79867</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1425,21 +1443,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1449,10 +1467,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>515764</v>
+        <v>515731</v>
       </c>
       <c r="R9" t="n">
-        <v>7004967</v>
+        <v>7004974</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1485,11 +1503,6 @@
       <c r="AA9" t="inlineStr">
         <is>
           <t>2025-03-20</t>
-        </is>
-      </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1516,10 +1529,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>123333791</v>
+        <v>123333794</v>
       </c>
       <c r="B10" t="n">
-        <v>79862</v>
+        <v>79867</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1556,10 +1569,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>515731</v>
+        <v>515718</v>
       </c>
       <c r="R10" t="n">
-        <v>7004974</v>
+        <v>7004917</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1618,10 +1631,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>123333779</v>
+        <v>123333789</v>
       </c>
       <c r="B11" t="n">
-        <v>57487</v>
+        <v>57490</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1658,10 +1671,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>515628</v>
+        <v>515716</v>
       </c>
       <c r="R11" t="n">
-        <v>7004943</v>
+        <v>7004917</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1728,7 +1741,7 @@
         <v>123333782</v>
       </c>
       <c r="B12" t="n">
-        <v>57487</v>
+        <v>57490</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1832,10 +1845,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>123333795</v>
+        <v>123333793</v>
       </c>
       <c r="B13" t="n">
-        <v>56689</v>
+        <v>79867</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1848,42 +1861,34 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>102612</v>
+        <v>6458</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K13" t="inlineStr"/>
-      <c r="L13" t="inlineStr"/>
-      <c r="M13" t="inlineStr"/>
-      <c r="N13" t="inlineStr"/>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
           <t>Näverbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>515669</v>
+        <v>515756</v>
       </c>
       <c r="R13" t="n">
-        <v>7005043</v>
+        <v>7004969</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1916,11 +1921,6 @@
       <c r="AA13" t="inlineStr">
         <is>
           <t>2025-03-20</t>
-        </is>
-      </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>minst 2 hörda</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1947,10 +1947,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>123333783</v>
+        <v>123333790</v>
       </c>
       <c r="B14" t="n">
-        <v>57487</v>
+        <v>79867</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1963,21 +1963,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1987,10 +1987,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>515764</v>
+        <v>515654</v>
       </c>
       <c r="R14" t="n">
-        <v>7004977</v>
+        <v>7005065</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2023,11 +2023,6 @@
       <c r="AA14" t="inlineStr">
         <is>
           <t>2025-03-20</t>
-        </is>
-      </c>
-      <c r="AC14" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2054,10 +2049,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>123333794</v>
+        <v>123333788</v>
       </c>
       <c r="B15" t="n">
-        <v>79862</v>
+        <v>57490</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2070,21 +2065,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2094,10 +2089,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>515718</v>
+        <v>515844</v>
       </c>
       <c r="R15" t="n">
-        <v>7004917</v>
+        <v>7004872</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2130,6 +2125,11 @@
       <c r="AA15" t="inlineStr">
         <is>
           <t>2025-03-20</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2156,10 +2156,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>123333784</v>
+        <v>123333785</v>
       </c>
       <c r="B16" t="n">
-        <v>57487</v>
+        <v>57490</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2196,10 +2196,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>515758</v>
+        <v>515764</v>
       </c>
       <c r="R16" t="n">
-        <v>7004972</v>
+        <v>7004967</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2236,7 +2236,7 @@
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2266,7 +2266,7 @@
         <v>123333781</v>
       </c>
       <c r="B17" t="n">
-        <v>57487</v>
+        <v>57490</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>

--- a/artfynd/A 58368-2024 artfynd.xlsx
+++ b/artfynd/A 58368-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>123333784</v>
       </c>
       <c r="B2" t="n">
-        <v>57490</v>
+        <v>57491</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -782,10 +782,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123333795</v>
+        <v>123333790</v>
       </c>
       <c r="B3" t="n">
-        <v>56692</v>
+        <v>79869</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -798,42 +798,34 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>102612</v>
+        <v>6458</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr"/>
-      <c r="N3" t="inlineStr"/>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
           <t>Näverbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>515669</v>
+        <v>515654</v>
       </c>
       <c r="R3" t="n">
-        <v>7005043</v>
+        <v>7005065</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -866,11 +858,6 @@
       <c r="AA3" t="inlineStr">
         <is>
           <t>2025-03-20</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>minst 2 hörda</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -897,10 +884,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123333792</v>
+        <v>123333783</v>
       </c>
       <c r="B4" t="n">
-        <v>79867</v>
+        <v>57491</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -913,21 +900,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -937,10 +924,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>515741</v>
+        <v>515764</v>
       </c>
       <c r="R4" t="n">
-        <v>7004964</v>
+        <v>7004977</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -973,6 +960,11 @@
       <c r="AA4" t="inlineStr">
         <is>
           <t>2025-03-20</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -999,10 +991,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>123333783</v>
+        <v>123333789</v>
       </c>
       <c r="B5" t="n">
-        <v>57490</v>
+        <v>57491</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1039,10 +1031,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>515764</v>
+        <v>515716</v>
       </c>
       <c r="R5" t="n">
-        <v>7004977</v>
+        <v>7004917</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1106,10 +1098,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>123333779</v>
+        <v>123333782</v>
       </c>
       <c r="B6" t="n">
-        <v>57490</v>
+        <v>57491</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1146,10 +1138,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>515628</v>
+        <v>515629</v>
       </c>
       <c r="R6" t="n">
-        <v>7004943</v>
+        <v>7004991</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1186,7 +1178,7 @@
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1213,10 +1205,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>123333787</v>
+        <v>123333793</v>
       </c>
       <c r="B7" t="n">
-        <v>57490</v>
+        <v>79869</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1229,21 +1221,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1253,10 +1245,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>515914</v>
+        <v>515756</v>
       </c>
       <c r="R7" t="n">
-        <v>7004901</v>
+        <v>7004969</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1289,11 +1281,6 @@
       <c r="AA7" t="inlineStr">
         <is>
           <t>2025-03-20</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1320,10 +1307,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>123333786</v>
+        <v>123333785</v>
       </c>
       <c r="B8" t="n">
-        <v>57490</v>
+        <v>57491</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1360,10 +1347,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>515911</v>
+        <v>515764</v>
       </c>
       <c r="R8" t="n">
-        <v>7004907</v>
+        <v>7004967</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1427,10 +1414,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>123333791</v>
+        <v>123333792</v>
       </c>
       <c r="B9" t="n">
-        <v>79867</v>
+        <v>79869</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1467,10 +1454,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>515731</v>
+        <v>515741</v>
       </c>
       <c r="R9" t="n">
-        <v>7004974</v>
+        <v>7004964</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1529,10 +1516,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>123333794</v>
+        <v>123333791</v>
       </c>
       <c r="B10" t="n">
-        <v>79867</v>
+        <v>79869</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1569,10 +1556,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>515718</v>
+        <v>515731</v>
       </c>
       <c r="R10" t="n">
-        <v>7004917</v>
+        <v>7004974</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1631,10 +1618,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>123333789</v>
+        <v>123333794</v>
       </c>
       <c r="B11" t="n">
-        <v>57490</v>
+        <v>79869</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1647,21 +1634,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1671,7 +1658,7 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>515716</v>
+        <v>515718</v>
       </c>
       <c r="R11" t="n">
         <v>7004917</v>
@@ -1707,11 +1694,6 @@
       <c r="AA11" t="inlineStr">
         <is>
           <t>2025-03-20</t>
-        </is>
-      </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1738,10 +1720,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>123333782</v>
+        <v>123333779</v>
       </c>
       <c r="B12" t="n">
-        <v>57490</v>
+        <v>57491</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1778,10 +1760,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>515629</v>
+        <v>515628</v>
       </c>
       <c r="R12" t="n">
-        <v>7004991</v>
+        <v>7004943</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1818,7 +1800,7 @@
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1845,10 +1827,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>123333793</v>
+        <v>123333787</v>
       </c>
       <c r="B13" t="n">
-        <v>79867</v>
+        <v>57491</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1861,21 +1843,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1885,10 +1867,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>515756</v>
+        <v>515914</v>
       </c>
       <c r="R13" t="n">
-        <v>7004969</v>
+        <v>7004901</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1921,6 +1903,11 @@
       <c r="AA13" t="inlineStr">
         <is>
           <t>2025-03-20</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1947,10 +1934,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>123333790</v>
+        <v>123333788</v>
       </c>
       <c r="B14" t="n">
-        <v>79867</v>
+        <v>57491</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1963,21 +1950,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1987,10 +1974,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>515654</v>
+        <v>515844</v>
       </c>
       <c r="R14" t="n">
-        <v>7005065</v>
+        <v>7004872</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2023,6 +2010,11 @@
       <c r="AA14" t="inlineStr">
         <is>
           <t>2025-03-20</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2049,10 +2041,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>123333788</v>
+        <v>123333786</v>
       </c>
       <c r="B15" t="n">
-        <v>57490</v>
+        <v>57491</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2089,10 +2081,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>515844</v>
+        <v>515911</v>
       </c>
       <c r="R15" t="n">
-        <v>7004872</v>
+        <v>7004907</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2156,10 +2148,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>123333785</v>
+        <v>123333781</v>
       </c>
       <c r="B16" t="n">
-        <v>57490</v>
+        <v>57491</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2196,10 +2188,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>515764</v>
+        <v>515661</v>
       </c>
       <c r="R16" t="n">
-        <v>7004967</v>
+        <v>7005038</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2263,10 +2255,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>123333781</v>
+        <v>123333795</v>
       </c>
       <c r="B17" t="n">
-        <v>57490</v>
+        <v>56692</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2279,16 +2271,16 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>100109</v>
+        <v>102612</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -2296,17 +2288,25 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I17" t="inlineStr"/>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr"/>
+      <c r="L17" t="inlineStr"/>
+      <c r="M17" t="inlineStr"/>
+      <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
           <t>Näverbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>515661</v>
+        <v>515669</v>
       </c>
       <c r="R17" t="n">
-        <v>7005038</v>
+        <v>7005043</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2343,7 +2343,7 @@
       </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>minst 2 hörda</t>
         </is>
       </c>
       <c r="AD17" t="b">

--- a/artfynd/A 58368-2024 artfynd.xlsx
+++ b/artfynd/A 58368-2024 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>123333784</v>
+        <v>123333785</v>
       </c>
       <c r="B2" t="n">
         <v>57491</v>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>515758</v>
+        <v>515764</v>
       </c>
       <c r="R2" t="n">
-        <v>7004972</v>
+        <v>7004967</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -755,7 +755,7 @@
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -782,10 +782,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123333790</v>
+        <v>123333786</v>
       </c>
       <c r="B3" t="n">
-        <v>79869</v>
+        <v>57491</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -798,21 +798,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -822,10 +822,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>515654</v>
+        <v>515911</v>
       </c>
       <c r="R3" t="n">
-        <v>7005065</v>
+        <v>7004907</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -858,6 +858,11 @@
       <c r="AA3" t="inlineStr">
         <is>
           <t>2025-03-20</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -884,10 +889,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123333783</v>
+        <v>123333791</v>
       </c>
       <c r="B4" t="n">
-        <v>57491</v>
+        <v>79869</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -900,21 +905,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -924,10 +929,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>515764</v>
+        <v>515731</v>
       </c>
       <c r="R4" t="n">
-        <v>7004977</v>
+        <v>7004974</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -960,11 +965,6 @@
       <c r="AA4" t="inlineStr">
         <is>
           <t>2025-03-20</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -991,10 +991,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>123333789</v>
+        <v>123333790</v>
       </c>
       <c r="B5" t="n">
-        <v>57491</v>
+        <v>79869</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1007,21 +1007,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1031,10 +1031,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>515716</v>
+        <v>515654</v>
       </c>
       <c r="R5" t="n">
-        <v>7004917</v>
+        <v>7005065</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1067,11 +1067,6 @@
       <c r="AA5" t="inlineStr">
         <is>
           <t>2025-03-20</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1098,10 +1093,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>123333782</v>
+        <v>123333795</v>
       </c>
       <c r="B6" t="n">
-        <v>57491</v>
+        <v>56692</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1114,16 +1109,16 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100109</v>
+        <v>102612</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -1131,17 +1126,25 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I6" t="inlineStr"/>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr"/>
+      <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
           <t>Näverbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>515629</v>
+        <v>515669</v>
       </c>
       <c r="R6" t="n">
-        <v>7004991</v>
+        <v>7005043</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1178,7 +1181,7 @@
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>minst 2 hörda</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1307,7 +1310,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>123333785</v>
+        <v>123333788</v>
       </c>
       <c r="B8" t="n">
         <v>57491</v>
@@ -1347,10 +1350,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>515764</v>
+        <v>515844</v>
       </c>
       <c r="R8" t="n">
-        <v>7004967</v>
+        <v>7004872</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1414,10 +1417,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>123333792</v>
+        <v>123333781</v>
       </c>
       <c r="B9" t="n">
-        <v>79869</v>
+        <v>57491</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1430,21 +1433,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1454,10 +1457,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>515741</v>
+        <v>515661</v>
       </c>
       <c r="R9" t="n">
-        <v>7004964</v>
+        <v>7005038</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1490,6 +1493,11 @@
       <c r="AA9" t="inlineStr">
         <is>
           <t>2025-03-20</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1516,10 +1524,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>123333791</v>
+        <v>123333784</v>
       </c>
       <c r="B10" t="n">
-        <v>79869</v>
+        <v>57491</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1532,21 +1540,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1556,10 +1564,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>515731</v>
+        <v>515758</v>
       </c>
       <c r="R10" t="n">
-        <v>7004974</v>
+        <v>7004972</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1592,6 +1600,11 @@
       <c r="AA10" t="inlineStr">
         <is>
           <t>2025-03-20</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1618,10 +1631,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>123333794</v>
+        <v>123333779</v>
       </c>
       <c r="B11" t="n">
-        <v>79869</v>
+        <v>57491</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1634,21 +1647,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1658,10 +1671,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>515718</v>
+        <v>515628</v>
       </c>
       <c r="R11" t="n">
-        <v>7004917</v>
+        <v>7004943</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1694,6 +1707,11 @@
       <c r="AA11" t="inlineStr">
         <is>
           <t>2025-03-20</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1720,10 +1738,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>123333779</v>
+        <v>123333794</v>
       </c>
       <c r="B12" t="n">
-        <v>57491</v>
+        <v>79869</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1736,21 +1754,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1760,10 +1778,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>515628</v>
+        <v>515718</v>
       </c>
       <c r="R12" t="n">
-        <v>7004943</v>
+        <v>7004917</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1796,11 +1814,6 @@
       <c r="AA12" t="inlineStr">
         <is>
           <t>2025-03-20</t>
-        </is>
-      </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1827,7 +1840,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>123333787</v>
+        <v>123333783</v>
       </c>
       <c r="B13" t="n">
         <v>57491</v>
@@ -1867,10 +1880,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>515914</v>
+        <v>515764</v>
       </c>
       <c r="R13" t="n">
-        <v>7004901</v>
+        <v>7004977</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1934,7 +1947,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>123333788</v>
+        <v>123333789</v>
       </c>
       <c r="B14" t="n">
         <v>57491</v>
@@ -1974,10 +1987,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>515844</v>
+        <v>515716</v>
       </c>
       <c r="R14" t="n">
-        <v>7004872</v>
+        <v>7004917</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2041,7 +2054,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>123333786</v>
+        <v>123333787</v>
       </c>
       <c r="B15" t="n">
         <v>57491</v>
@@ -2081,10 +2094,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>515911</v>
+        <v>515914</v>
       </c>
       <c r="R15" t="n">
-        <v>7004907</v>
+        <v>7004901</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2148,7 +2161,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>123333781</v>
+        <v>123333782</v>
       </c>
       <c r="B16" t="n">
         <v>57491</v>
@@ -2188,10 +2201,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>515661</v>
+        <v>515629</v>
       </c>
       <c r="R16" t="n">
-        <v>7005038</v>
+        <v>7004991</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2228,7 +2241,7 @@
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2255,10 +2268,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>123333795</v>
+        <v>123333792</v>
       </c>
       <c r="B17" t="n">
-        <v>56692</v>
+        <v>79869</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2271,42 +2284,34 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>102612</v>
+        <v>6458</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K17" t="inlineStr"/>
-      <c r="L17" t="inlineStr"/>
-      <c r="M17" t="inlineStr"/>
-      <c r="N17" t="inlineStr"/>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
           <t>Näverbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>515669</v>
+        <v>515741</v>
       </c>
       <c r="R17" t="n">
-        <v>7005043</v>
+        <v>7004964</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2339,11 +2344,6 @@
       <c r="AA17" t="inlineStr">
         <is>
           <t>2025-03-20</t>
-        </is>
-      </c>
-      <c r="AC17" t="inlineStr">
-        <is>
-          <t>minst 2 hörda</t>
         </is>
       </c>
       <c r="AD17" t="b">

--- a/artfynd/A 58368-2024 artfynd.xlsx
+++ b/artfynd/A 58368-2024 artfynd.xlsx
@@ -991,10 +991,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>123333790</v>
+        <v>123333795</v>
       </c>
       <c r="B5" t="n">
-        <v>79869</v>
+        <v>56692</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1007,34 +1007,42 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6458</v>
+        <v>102612</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr"/>
+      <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
           <t>Näverbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>515654</v>
+        <v>515669</v>
       </c>
       <c r="R5" t="n">
-        <v>7005065</v>
+        <v>7005043</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1067,6 +1075,11 @@
       <c r="AA5" t="inlineStr">
         <is>
           <t>2025-03-20</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>minst 2 hörda</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1093,10 +1106,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>123333795</v>
+        <v>123333790</v>
       </c>
       <c r="B6" t="n">
-        <v>56692</v>
+        <v>79869</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1109,42 +1122,34 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>102612</v>
+        <v>6458</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr"/>
-      <c r="M6" t="inlineStr"/>
-      <c r="N6" t="inlineStr"/>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
           <t>Näverbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>515669</v>
+        <v>515654</v>
       </c>
       <c r="R6" t="n">
-        <v>7005043</v>
+        <v>7005065</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1177,11 +1182,6 @@
       <c r="AA6" t="inlineStr">
         <is>
           <t>2025-03-20</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>minst 2 hörda</t>
         </is>
       </c>
       <c r="AD6" t="b">

--- a/artfynd/A 58368-2024 artfynd.xlsx
+++ b/artfynd/A 58368-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>123333785</v>
+        <v>123333792</v>
       </c>
       <c r="B2" t="n">
-        <v>57491</v>
+        <v>79869</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>515764</v>
+        <v>515741</v>
       </c>
       <c r="R2" t="n">
-        <v>7004967</v>
+        <v>7004964</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -751,11 +751,6 @@
       <c r="AA2" t="inlineStr">
         <is>
           <t>2025-03-20</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -782,7 +777,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123333786</v>
+        <v>123333783</v>
       </c>
       <c r="B3" t="n">
         <v>57491</v>
@@ -822,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>515911</v>
+        <v>515764</v>
       </c>
       <c r="R3" t="n">
-        <v>7004907</v>
+        <v>7004977</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -889,10 +884,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123333791</v>
+        <v>123333786</v>
       </c>
       <c r="B4" t="n">
-        <v>79869</v>
+        <v>57491</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -905,21 +900,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -929,10 +924,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>515731</v>
+        <v>515911</v>
       </c>
       <c r="R4" t="n">
-        <v>7004974</v>
+        <v>7004907</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -965,6 +960,11 @@
       <c r="AA4" t="inlineStr">
         <is>
           <t>2025-03-20</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -991,10 +991,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>123333795</v>
+        <v>123333793</v>
       </c>
       <c r="B5" t="n">
-        <v>56692</v>
+        <v>79869</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1007,42 +1007,34 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>102612</v>
+        <v>6458</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
-      <c r="M5" t="inlineStr"/>
-      <c r="N5" t="inlineStr"/>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
           <t>Näverbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>515669</v>
+        <v>515756</v>
       </c>
       <c r="R5" t="n">
-        <v>7005043</v>
+        <v>7004969</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1075,11 +1067,6 @@
       <c r="AA5" t="inlineStr">
         <is>
           <t>2025-03-20</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>minst 2 hörda</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1106,7 +1093,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>123333790</v>
+        <v>123333794</v>
       </c>
       <c r="B6" t="n">
         <v>79869</v>
@@ -1146,10 +1133,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>515654</v>
+        <v>515718</v>
       </c>
       <c r="R6" t="n">
-        <v>7005065</v>
+        <v>7004917</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1208,10 +1195,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>123333793</v>
+        <v>123333784</v>
       </c>
       <c r="B7" t="n">
-        <v>79869</v>
+        <v>57491</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1224,21 +1211,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1248,10 +1235,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>515756</v>
+        <v>515758</v>
       </c>
       <c r="R7" t="n">
-        <v>7004969</v>
+        <v>7004972</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1284,6 +1271,11 @@
       <c r="AA7" t="inlineStr">
         <is>
           <t>2025-03-20</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1310,7 +1302,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>123333788</v>
+        <v>123333787</v>
       </c>
       <c r="B8" t="n">
         <v>57491</v>
@@ -1350,10 +1342,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>515844</v>
+        <v>515914</v>
       </c>
       <c r="R8" t="n">
-        <v>7004872</v>
+        <v>7004901</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1417,7 +1409,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>123333781</v>
+        <v>123333788</v>
       </c>
       <c r="B9" t="n">
         <v>57491</v>
@@ -1457,10 +1449,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>515661</v>
+        <v>515844</v>
       </c>
       <c r="R9" t="n">
-        <v>7005038</v>
+        <v>7004872</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1524,10 +1516,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>123333784</v>
+        <v>123333790</v>
       </c>
       <c r="B10" t="n">
-        <v>57491</v>
+        <v>79869</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1540,21 +1532,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1564,10 +1556,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>515758</v>
+        <v>515654</v>
       </c>
       <c r="R10" t="n">
-        <v>7004972</v>
+        <v>7005065</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1600,11 +1592,6 @@
       <c r="AA10" t="inlineStr">
         <is>
           <t>2025-03-20</t>
-        </is>
-      </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1631,7 +1618,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>123333779</v>
+        <v>123333781</v>
       </c>
       <c r="B11" t="n">
         <v>57491</v>
@@ -1671,10 +1658,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>515628</v>
+        <v>515661</v>
       </c>
       <c r="R11" t="n">
-        <v>7004943</v>
+        <v>7005038</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1738,10 +1725,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>123333794</v>
+        <v>123333782</v>
       </c>
       <c r="B12" t="n">
-        <v>79869</v>
+        <v>57491</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1754,21 +1741,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1778,10 +1765,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>515718</v>
+        <v>515629</v>
       </c>
       <c r="R12" t="n">
-        <v>7004917</v>
+        <v>7004991</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1814,6 +1801,11 @@
       <c r="AA12" t="inlineStr">
         <is>
           <t>2025-03-20</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1840,7 +1832,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>123333783</v>
+        <v>123333785</v>
       </c>
       <c r="B13" t="n">
         <v>57491</v>
@@ -1883,7 +1875,7 @@
         <v>515764</v>
       </c>
       <c r="R13" t="n">
-        <v>7004977</v>
+        <v>7004967</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1947,7 +1939,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>123333789</v>
+        <v>123333779</v>
       </c>
       <c r="B14" t="n">
         <v>57491</v>
@@ -1987,10 +1979,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>515716</v>
+        <v>515628</v>
       </c>
       <c r="R14" t="n">
-        <v>7004917</v>
+        <v>7004943</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2054,10 +2046,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>123333787</v>
+        <v>123333791</v>
       </c>
       <c r="B15" t="n">
-        <v>57491</v>
+        <v>79869</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2070,21 +2062,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2094,10 +2086,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>515914</v>
+        <v>515731</v>
       </c>
       <c r="R15" t="n">
-        <v>7004901</v>
+        <v>7004974</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2130,11 +2122,6 @@
       <c r="AA15" t="inlineStr">
         <is>
           <t>2025-03-20</t>
-        </is>
-      </c>
-      <c r="AC15" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2161,7 +2148,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>123333782</v>
+        <v>123333789</v>
       </c>
       <c r="B16" t="n">
         <v>57491</v>
@@ -2201,10 +2188,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>515629</v>
+        <v>515716</v>
       </c>
       <c r="R16" t="n">
-        <v>7004991</v>
+        <v>7004917</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2241,7 +2228,7 @@
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2268,10 +2255,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>123333792</v>
+        <v>123333795</v>
       </c>
       <c r="B17" t="n">
-        <v>79869</v>
+        <v>56692</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2284,34 +2271,42 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6458</v>
+        <v>102612</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr"/>
+      <c r="L17" t="inlineStr"/>
+      <c r="M17" t="inlineStr"/>
+      <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
           <t>Näverbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>515741</v>
+        <v>515669</v>
       </c>
       <c r="R17" t="n">
-        <v>7004964</v>
+        <v>7005043</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2344,6 +2339,11 @@
       <c r="AA17" t="inlineStr">
         <is>
           <t>2025-03-20</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>minst 2 hörda</t>
         </is>
       </c>
       <c r="AD17" t="b">

--- a/artfynd/A 58368-2024 artfynd.xlsx
+++ b/artfynd/A 58368-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>123333792</v>
+        <v>123333783</v>
       </c>
       <c r="B2" t="n">
-        <v>79869</v>
+        <v>57491</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>515741</v>
+        <v>515764</v>
       </c>
       <c r="R2" t="n">
-        <v>7004964</v>
+        <v>7004977</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -751,6 +751,11 @@
       <c r="AA2" t="inlineStr">
         <is>
           <t>2025-03-20</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -777,7 +782,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123333783</v>
+        <v>123333784</v>
       </c>
       <c r="B3" t="n">
         <v>57491</v>
@@ -817,10 +822,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>515764</v>
+        <v>515758</v>
       </c>
       <c r="R3" t="n">
-        <v>7004977</v>
+        <v>7004972</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -857,7 +862,7 @@
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -884,10 +889,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123333786</v>
+        <v>123333795</v>
       </c>
       <c r="B4" t="n">
-        <v>57491</v>
+        <v>56692</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -900,16 +905,16 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100109</v>
+        <v>102612</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -917,17 +922,25 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I4" t="inlineStr"/>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr"/>
+      <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
           <t>Näverbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>515911</v>
+        <v>515669</v>
       </c>
       <c r="R4" t="n">
-        <v>7004907</v>
+        <v>7005043</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -964,7 +977,7 @@
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>minst 2 hörda</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -991,7 +1004,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>123333793</v>
+        <v>123333792</v>
       </c>
       <c r="B5" t="n">
         <v>79869</v>
@@ -1031,10 +1044,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>515756</v>
+        <v>515741</v>
       </c>
       <c r="R5" t="n">
-        <v>7004969</v>
+        <v>7004964</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1093,10 +1106,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>123333794</v>
+        <v>123333782</v>
       </c>
       <c r="B6" t="n">
-        <v>79869</v>
+        <v>57491</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1109,21 +1122,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1133,10 +1146,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>515718</v>
+        <v>515629</v>
       </c>
       <c r="R6" t="n">
-        <v>7004917</v>
+        <v>7004991</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1169,6 +1182,11 @@
       <c r="AA6" t="inlineStr">
         <is>
           <t>2025-03-20</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1195,10 +1213,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>123333784</v>
+        <v>123333794</v>
       </c>
       <c r="B7" t="n">
-        <v>57491</v>
+        <v>79869</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1211,21 +1229,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1235,10 +1253,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>515758</v>
+        <v>515718</v>
       </c>
       <c r="R7" t="n">
-        <v>7004972</v>
+        <v>7004917</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1271,11 +1289,6 @@
       <c r="AA7" t="inlineStr">
         <is>
           <t>2025-03-20</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1409,10 +1422,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>123333788</v>
+        <v>123333790</v>
       </c>
       <c r="B9" t="n">
-        <v>57491</v>
+        <v>79869</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1425,21 +1438,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1449,10 +1462,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>515844</v>
+        <v>515654</v>
       </c>
       <c r="R9" t="n">
-        <v>7004872</v>
+        <v>7005065</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1485,11 +1498,6 @@
       <c r="AA9" t="inlineStr">
         <is>
           <t>2025-03-20</t>
-        </is>
-      </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1516,10 +1524,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>123333790</v>
+        <v>123333789</v>
       </c>
       <c r="B10" t="n">
-        <v>79869</v>
+        <v>57491</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1532,21 +1540,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1556,10 +1564,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>515654</v>
+        <v>515716</v>
       </c>
       <c r="R10" t="n">
-        <v>7005065</v>
+        <v>7004917</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1592,6 +1600,11 @@
       <c r="AA10" t="inlineStr">
         <is>
           <t>2025-03-20</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1618,7 +1631,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>123333781</v>
+        <v>123333788</v>
       </c>
       <c r="B11" t="n">
         <v>57491</v>
@@ -1658,10 +1671,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>515661</v>
+        <v>515844</v>
       </c>
       <c r="R11" t="n">
-        <v>7005038</v>
+        <v>7004872</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1725,7 +1738,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>123333782</v>
+        <v>123333779</v>
       </c>
       <c r="B12" t="n">
         <v>57491</v>
@@ -1765,10 +1778,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>515629</v>
+        <v>515628</v>
       </c>
       <c r="R12" t="n">
-        <v>7004991</v>
+        <v>7004943</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1805,7 +1818,7 @@
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1832,10 +1845,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>123333785</v>
+        <v>123333793</v>
       </c>
       <c r="B13" t="n">
-        <v>57491</v>
+        <v>79869</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1848,21 +1861,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1872,10 +1885,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>515764</v>
+        <v>515756</v>
       </c>
       <c r="R13" t="n">
-        <v>7004967</v>
+        <v>7004969</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1908,11 +1921,6 @@
       <c r="AA13" t="inlineStr">
         <is>
           <t>2025-03-20</t>
-        </is>
-      </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1939,10 +1947,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>123333779</v>
+        <v>123333791</v>
       </c>
       <c r="B14" t="n">
-        <v>57491</v>
+        <v>79869</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1955,21 +1963,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1979,10 +1987,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>515628</v>
+        <v>515731</v>
       </c>
       <c r="R14" t="n">
-        <v>7004943</v>
+        <v>7004974</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2015,11 +2023,6 @@
       <c r="AA14" t="inlineStr">
         <is>
           <t>2025-03-20</t>
-        </is>
-      </c>
-      <c r="AC14" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2046,10 +2049,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>123333791</v>
+        <v>123333786</v>
       </c>
       <c r="B15" t="n">
-        <v>79869</v>
+        <v>57491</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2062,21 +2065,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2086,10 +2089,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>515731</v>
+        <v>515911</v>
       </c>
       <c r="R15" t="n">
-        <v>7004974</v>
+        <v>7004907</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2122,6 +2125,11 @@
       <c r="AA15" t="inlineStr">
         <is>
           <t>2025-03-20</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2148,7 +2156,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>123333789</v>
+        <v>123333781</v>
       </c>
       <c r="B16" t="n">
         <v>57491</v>
@@ -2188,10 +2196,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>515716</v>
+        <v>515661</v>
       </c>
       <c r="R16" t="n">
-        <v>7004917</v>
+        <v>7005038</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2255,10 +2263,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>123333795</v>
+        <v>123333785</v>
       </c>
       <c r="B17" t="n">
-        <v>56692</v>
+        <v>57491</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2271,16 +2279,16 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>102612</v>
+        <v>100109</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -2288,25 +2296,17 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K17" t="inlineStr"/>
-      <c r="L17" t="inlineStr"/>
-      <c r="M17" t="inlineStr"/>
-      <c r="N17" t="inlineStr"/>
+      <c r="I17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
           <t>Näverbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>515669</v>
+        <v>515764</v>
       </c>
       <c r="R17" t="n">
-        <v>7005043</v>
+        <v>7004967</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2343,7 +2343,7 @@
       </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>minst 2 hörda</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD17" t="b">

--- a/artfynd/A 58368-2024 artfynd.xlsx
+++ b/artfynd/A 58368-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>123333783</v>
+        <v>123333795</v>
       </c>
       <c r="B2" t="n">
-        <v>57491</v>
+        <v>56692</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,16 +691,16 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100109</v>
+        <v>102612</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -708,17 +708,25 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I2" t="inlineStr"/>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr"/>
+      <c r="M2" t="inlineStr"/>
+      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
           <t>Näverbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>515764</v>
+        <v>515669</v>
       </c>
       <c r="R2" t="n">
-        <v>7004977</v>
+        <v>7005043</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -755,7 +763,7 @@
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>minst 2 hörda</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -782,10 +790,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123333784</v>
+        <v>123333790</v>
       </c>
       <c r="B3" t="n">
-        <v>57491</v>
+        <v>79869</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -798,21 +806,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -822,10 +830,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>515758</v>
+        <v>515654</v>
       </c>
       <c r="R3" t="n">
-        <v>7004972</v>
+        <v>7005065</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -858,11 +866,6 @@
       <c r="AA3" t="inlineStr">
         <is>
           <t>2025-03-20</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -889,10 +892,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123333795</v>
+        <v>123333789</v>
       </c>
       <c r="B4" t="n">
-        <v>56692</v>
+        <v>57491</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -905,16 +908,16 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>102612</v>
+        <v>100109</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -922,25 +925,17 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr"/>
-      <c r="N4" t="inlineStr"/>
+      <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
           <t>Näverbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>515669</v>
+        <v>515716</v>
       </c>
       <c r="R4" t="n">
-        <v>7005043</v>
+        <v>7004917</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -977,7 +972,7 @@
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>minst 2 hörda</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1106,10 +1101,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>123333782</v>
+        <v>123333794</v>
       </c>
       <c r="B6" t="n">
-        <v>57491</v>
+        <v>79869</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1122,21 +1117,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1146,10 +1141,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>515629</v>
+        <v>515718</v>
       </c>
       <c r="R6" t="n">
-        <v>7004991</v>
+        <v>7004917</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1182,11 +1177,6 @@
       <c r="AA6" t="inlineStr">
         <is>
           <t>2025-03-20</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1213,7 +1203,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>123333794</v>
+        <v>123333791</v>
       </c>
       <c r="B7" t="n">
         <v>79869</v>
@@ -1253,10 +1243,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>515718</v>
+        <v>515731</v>
       </c>
       <c r="R7" t="n">
-        <v>7004917</v>
+        <v>7004974</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1315,7 +1305,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>123333787</v>
+        <v>123333783</v>
       </c>
       <c r="B8" t="n">
         <v>57491</v>
@@ -1355,10 +1345,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>515914</v>
+        <v>515764</v>
       </c>
       <c r="R8" t="n">
-        <v>7004901</v>
+        <v>7004977</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1422,10 +1412,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>123333790</v>
+        <v>123333779</v>
       </c>
       <c r="B9" t="n">
-        <v>79869</v>
+        <v>57491</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1438,21 +1428,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1462,10 +1452,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>515654</v>
+        <v>515628</v>
       </c>
       <c r="R9" t="n">
-        <v>7005065</v>
+        <v>7004943</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1498,6 +1488,11 @@
       <c r="AA9" t="inlineStr">
         <is>
           <t>2025-03-20</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1524,10 +1519,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>123333789</v>
+        <v>123333793</v>
       </c>
       <c r="B10" t="n">
-        <v>57491</v>
+        <v>79869</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1540,21 +1535,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1564,10 +1559,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>515716</v>
+        <v>515756</v>
       </c>
       <c r="R10" t="n">
-        <v>7004917</v>
+        <v>7004969</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1600,11 +1595,6 @@
       <c r="AA10" t="inlineStr">
         <is>
           <t>2025-03-20</t>
-        </is>
-      </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1631,7 +1621,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>123333788</v>
+        <v>123333782</v>
       </c>
       <c r="B11" t="n">
         <v>57491</v>
@@ -1671,10 +1661,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>515844</v>
+        <v>515629</v>
       </c>
       <c r="R11" t="n">
-        <v>7004872</v>
+        <v>7004991</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1711,7 +1701,7 @@
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1738,7 +1728,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>123333779</v>
+        <v>123333781</v>
       </c>
       <c r="B12" t="n">
         <v>57491</v>
@@ -1778,10 +1768,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>515628</v>
+        <v>515661</v>
       </c>
       <c r="R12" t="n">
-        <v>7004943</v>
+        <v>7005038</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1845,10 +1835,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>123333793</v>
+        <v>123333787</v>
       </c>
       <c r="B13" t="n">
-        <v>79869</v>
+        <v>57491</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1861,21 +1851,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1885,10 +1875,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>515756</v>
+        <v>515914</v>
       </c>
       <c r="R13" t="n">
-        <v>7004969</v>
+        <v>7004901</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1921,6 +1911,11 @@
       <c r="AA13" t="inlineStr">
         <is>
           <t>2025-03-20</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1947,10 +1942,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>123333791</v>
+        <v>123333786</v>
       </c>
       <c r="B14" t="n">
-        <v>79869</v>
+        <v>57491</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1963,21 +1958,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1987,10 +1982,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>515731</v>
+        <v>515911</v>
       </c>
       <c r="R14" t="n">
-        <v>7004974</v>
+        <v>7004907</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2023,6 +2018,11 @@
       <c r="AA14" t="inlineStr">
         <is>
           <t>2025-03-20</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2049,7 +2049,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>123333786</v>
+        <v>123333785</v>
       </c>
       <c r="B15" t="n">
         <v>57491</v>
@@ -2089,10 +2089,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>515911</v>
+        <v>515764</v>
       </c>
       <c r="R15" t="n">
-        <v>7004907</v>
+        <v>7004967</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2156,7 +2156,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>123333781</v>
+        <v>123333788</v>
       </c>
       <c r="B16" t="n">
         <v>57491</v>
@@ -2196,10 +2196,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>515661</v>
+        <v>515844</v>
       </c>
       <c r="R16" t="n">
-        <v>7005038</v>
+        <v>7004872</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2263,7 +2263,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>123333785</v>
+        <v>123333784</v>
       </c>
       <c r="B17" t="n">
         <v>57491</v>
@@ -2303,10 +2303,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>515764</v>
+        <v>515758</v>
       </c>
       <c r="R17" t="n">
-        <v>7004967</v>
+        <v>7004972</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2343,7 +2343,7 @@
       </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD17" t="b">

--- a/artfynd/A 58368-2024 artfynd.xlsx
+++ b/artfynd/A 58368-2024 artfynd.xlsx
@@ -1519,10 +1519,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>123333793</v>
+        <v>123333782</v>
       </c>
       <c r="B10" t="n">
-        <v>79869</v>
+        <v>57491</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1535,21 +1535,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1559,10 +1559,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>515756</v>
+        <v>515629</v>
       </c>
       <c r="R10" t="n">
-        <v>7004969</v>
+        <v>7004991</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1595,6 +1595,11 @@
       <c r="AA10" t="inlineStr">
         <is>
           <t>2025-03-20</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1621,7 +1626,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>123333782</v>
+        <v>123333781</v>
       </c>
       <c r="B11" t="n">
         <v>57491</v>
@@ -1661,10 +1666,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>515629</v>
+        <v>515661</v>
       </c>
       <c r="R11" t="n">
-        <v>7004991</v>
+        <v>7005038</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1701,7 +1706,7 @@
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1728,7 +1733,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>123333781</v>
+        <v>123333787</v>
       </c>
       <c r="B12" t="n">
         <v>57491</v>
@@ -1768,10 +1773,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>515661</v>
+        <v>515914</v>
       </c>
       <c r="R12" t="n">
-        <v>7005038</v>
+        <v>7004901</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1835,10 +1840,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>123333787</v>
+        <v>123333793</v>
       </c>
       <c r="B13" t="n">
-        <v>57491</v>
+        <v>79869</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1851,21 +1856,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1875,10 +1880,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>515914</v>
+        <v>515756</v>
       </c>
       <c r="R13" t="n">
-        <v>7004901</v>
+        <v>7004969</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1911,11 +1916,6 @@
       <c r="AA13" t="inlineStr">
         <is>
           <t>2025-03-20</t>
-        </is>
-      </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD13" t="b">

--- a/artfynd/A 58368-2024 artfynd.xlsx
+++ b/artfynd/A 58368-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>123333795</v>
+        <v>123333783</v>
       </c>
       <c r="B2" t="n">
-        <v>56692</v>
+        <v>57491</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,16 +691,16 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>102612</v>
+        <v>100109</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -708,25 +708,17 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr"/>
-      <c r="N2" t="inlineStr"/>
+      <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
           <t>Näverbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>515669</v>
+        <v>515764</v>
       </c>
       <c r="R2" t="n">
-        <v>7005043</v>
+        <v>7004977</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -763,7 +755,7 @@
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>minst 2 hörda</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -790,7 +782,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123333790</v>
+        <v>123333793</v>
       </c>
       <c r="B3" t="n">
         <v>79869</v>
@@ -830,10 +822,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>515654</v>
+        <v>515756</v>
       </c>
       <c r="R3" t="n">
-        <v>7005065</v>
+        <v>7004969</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -892,7 +884,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123333789</v>
+        <v>123333786</v>
       </c>
       <c r="B4" t="n">
         <v>57491</v>
@@ -932,10 +924,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>515716</v>
+        <v>515911</v>
       </c>
       <c r="R4" t="n">
-        <v>7004917</v>
+        <v>7004907</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1101,7 +1093,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>123333794</v>
+        <v>123333791</v>
       </c>
       <c r="B6" t="n">
         <v>79869</v>
@@ -1141,10 +1133,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>515718</v>
+        <v>515731</v>
       </c>
       <c r="R6" t="n">
-        <v>7004917</v>
+        <v>7004974</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1203,7 +1195,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>123333791</v>
+        <v>123333790</v>
       </c>
       <c r="B7" t="n">
         <v>79869</v>
@@ -1243,10 +1235,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>515731</v>
+        <v>515654</v>
       </c>
       <c r="R7" t="n">
-        <v>7004974</v>
+        <v>7005065</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1305,7 +1297,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>123333783</v>
+        <v>123333785</v>
       </c>
       <c r="B8" t="n">
         <v>57491</v>
@@ -1348,7 +1340,7 @@
         <v>515764</v>
       </c>
       <c r="R8" t="n">
-        <v>7004977</v>
+        <v>7004967</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1412,7 +1404,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>123333779</v>
+        <v>123333787</v>
       </c>
       <c r="B9" t="n">
         <v>57491</v>
@@ -1452,10 +1444,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>515628</v>
+        <v>515914</v>
       </c>
       <c r="R9" t="n">
-        <v>7004943</v>
+        <v>7004901</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1519,7 +1511,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>123333782</v>
+        <v>123333781</v>
       </c>
       <c r="B10" t="n">
         <v>57491</v>
@@ -1559,10 +1551,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>515629</v>
+        <v>515661</v>
       </c>
       <c r="R10" t="n">
-        <v>7004991</v>
+        <v>7005038</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1599,7 +1591,7 @@
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1626,10 +1618,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>123333781</v>
+        <v>123333795</v>
       </c>
       <c r="B11" t="n">
-        <v>57491</v>
+        <v>56692</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1642,16 +1634,16 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100109</v>
+        <v>102612</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -1659,17 +1651,25 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I11" t="inlineStr"/>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr"/>
+      <c r="M11" t="inlineStr"/>
+      <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
           <t>Näverbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>515661</v>
+        <v>515669</v>
       </c>
       <c r="R11" t="n">
-        <v>7005038</v>
+        <v>7005043</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1706,7 +1706,7 @@
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>minst 2 hörda</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1733,7 +1733,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>123333787</v>
+        <v>123333782</v>
       </c>
       <c r="B12" t="n">
         <v>57491</v>
@@ -1773,10 +1773,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>515914</v>
+        <v>515629</v>
       </c>
       <c r="R12" t="n">
-        <v>7004901</v>
+        <v>7004991</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1813,7 +1813,7 @@
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1840,7 +1840,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>123333793</v>
+        <v>123333794</v>
       </c>
       <c r="B13" t="n">
         <v>79869</v>
@@ -1880,10 +1880,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>515756</v>
+        <v>515718</v>
       </c>
       <c r="R13" t="n">
-        <v>7004969</v>
+        <v>7004917</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1942,7 +1942,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>123333786</v>
+        <v>123333779</v>
       </c>
       <c r="B14" t="n">
         <v>57491</v>
@@ -1982,10 +1982,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>515911</v>
+        <v>515628</v>
       </c>
       <c r="R14" t="n">
-        <v>7004907</v>
+        <v>7004943</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2049,7 +2049,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>123333785</v>
+        <v>123333788</v>
       </c>
       <c r="B15" t="n">
         <v>57491</v>
@@ -2089,10 +2089,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>515764</v>
+        <v>515844</v>
       </c>
       <c r="R15" t="n">
-        <v>7004967</v>
+        <v>7004872</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2156,7 +2156,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>123333788</v>
+        <v>123333789</v>
       </c>
       <c r="B16" t="n">
         <v>57491</v>
@@ -2196,10 +2196,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>515844</v>
+        <v>515716</v>
       </c>
       <c r="R16" t="n">
-        <v>7004872</v>
+        <v>7004917</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>

--- a/artfynd/A 58368-2024 artfynd.xlsx
+++ b/artfynd/A 58368-2024 artfynd.xlsx
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>123333783</v>
+        <v>123333790</v>
       </c>
       <c r="B2" t="n">
-        <v>57491</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>515764</v>
+        <v>515654</v>
       </c>
       <c r="R2" t="n">
-        <v>7004977</v>
+        <v>7005065</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -751,11 +746,6 @@
       <c r="AA2" t="inlineStr">
         <is>
           <t>2025-03-20</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -782,15 +772,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123333793</v>
+        <v>123333791</v>
       </c>
       <c r="B3" t="n">
-        <v>79869</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -822,10 +807,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>515756</v>
+        <v>515731</v>
       </c>
       <c r="R3" t="n">
-        <v>7004969</v>
+        <v>7004974</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -884,15 +869,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123333786</v>
+        <v>123333792</v>
       </c>
       <c r="B4" t="n">
-        <v>57491</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -900,21 +880,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -924,10 +904,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>515911</v>
+        <v>515741</v>
       </c>
       <c r="R4" t="n">
-        <v>7004907</v>
+        <v>7004964</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -960,11 +940,6 @@
       <c r="AA4" t="inlineStr">
         <is>
           <t>2025-03-20</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -991,15 +966,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>123333792</v>
+        <v>123333793</v>
       </c>
       <c r="B5" t="n">
-        <v>79869</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1031,10 +1001,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>515741</v>
+        <v>515756</v>
       </c>
       <c r="R5" t="n">
-        <v>7004964</v>
+        <v>7004969</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1093,15 +1063,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>123333791</v>
+        <v>123333794</v>
       </c>
       <c r="B6" t="n">
-        <v>79869</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1133,10 +1098,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>515731</v>
+        <v>515718</v>
       </c>
       <c r="R6" t="n">
-        <v>7004974</v>
+        <v>7004917</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1195,15 +1160,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>123333790</v>
+        <v>123333779</v>
       </c>
       <c r="B7" t="n">
-        <v>79869</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1211,21 +1171,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1235,10 +1195,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>515654</v>
+        <v>515628</v>
       </c>
       <c r="R7" t="n">
-        <v>7005065</v>
+        <v>7004943</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1271,6 +1231,11 @@
       <c r="AA7" t="inlineStr">
         <is>
           <t>2025-03-20</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1297,15 +1262,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>123333785</v>
+        <v>123333781</v>
       </c>
       <c r="B8" t="n">
-        <v>57491</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1337,10 +1297,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>515764</v>
+        <v>515661</v>
       </c>
       <c r="R8" t="n">
-        <v>7004967</v>
+        <v>7005038</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1404,15 +1364,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>123333787</v>
+        <v>123333782</v>
       </c>
       <c r="B9" t="n">
-        <v>57491</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1444,10 +1399,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>515914</v>
+        <v>515629</v>
       </c>
       <c r="R9" t="n">
-        <v>7004901</v>
+        <v>7004991</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1484,7 +1439,7 @@
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1511,15 +1466,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>123333781</v>
+        <v>123333783</v>
       </c>
       <c r="B10" t="n">
-        <v>57491</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1551,10 +1501,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>515661</v>
+        <v>515764</v>
       </c>
       <c r="R10" t="n">
-        <v>7005038</v>
+        <v>7004977</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1618,15 +1568,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>123333795</v>
+        <v>123333784</v>
       </c>
       <c r="B11" t="n">
-        <v>56692</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1634,16 +1579,16 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>102612</v>
+        <v>100109</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -1651,25 +1596,17 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K11" t="inlineStr"/>
-      <c r="L11" t="inlineStr"/>
-      <c r="M11" t="inlineStr"/>
-      <c r="N11" t="inlineStr"/>
+      <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
           <t>Näverbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>515669</v>
+        <v>515758</v>
       </c>
       <c r="R11" t="n">
-        <v>7005043</v>
+        <v>7004972</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1706,7 +1643,7 @@
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>minst 2 hörda</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1733,15 +1670,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>123333782</v>
+        <v>123333785</v>
       </c>
       <c r="B12" t="n">
-        <v>57491</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1773,10 +1705,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>515629</v>
+        <v>515764</v>
       </c>
       <c r="R12" t="n">
-        <v>7004991</v>
+        <v>7004967</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1813,7 +1745,7 @@
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1840,15 +1772,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>123333794</v>
+        <v>123333786</v>
       </c>
       <c r="B13" t="n">
-        <v>79869</v>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1856,21 +1783,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1880,10 +1807,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>515718</v>
+        <v>515911</v>
       </c>
       <c r="R13" t="n">
-        <v>7004917</v>
+        <v>7004907</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1916,6 +1843,11 @@
       <c r="AA13" t="inlineStr">
         <is>
           <t>2025-03-20</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1942,15 +1874,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>123333779</v>
+        <v>123333787</v>
       </c>
       <c r="B14" t="n">
-        <v>57491</v>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1982,10 +1909,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>515628</v>
+        <v>515914</v>
       </c>
       <c r="R14" t="n">
-        <v>7004943</v>
+        <v>7004901</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2052,12 +1979,7 @@
         <v>123333788</v>
       </c>
       <c r="B15" t="n">
-        <v>57491</v>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2159,12 +2081,7 @@
         <v>123333789</v>
       </c>
       <c r="B16" t="n">
-        <v>57491</v>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2263,32 +2180,27 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>123333784</v>
+        <v>123333795</v>
       </c>
       <c r="B17" t="n">
-        <v>57491</v>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57132</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>100109</v>
+        <v>102612</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -2296,17 +2208,25 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I17" t="inlineStr"/>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr"/>
+      <c r="L17" t="inlineStr"/>
+      <c r="M17" t="inlineStr"/>
+      <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
           <t>Näverbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>515758</v>
+        <v>515669</v>
       </c>
       <c r="R17" t="n">
-        <v>7004972</v>
+        <v>7005043</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2343,7 +2263,7 @@
       </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>minst 2 hörda</t>
         </is>
       </c>
       <c r="AD17" t="b">

--- a/artfynd/A 58368-2024 artfynd.xlsx
+++ b/artfynd/A 58368-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY17"/>
+  <dimension ref="A1:AZ17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -769,6 +774,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123333790</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -866,6 +876,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123333791</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -963,6 +978,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123333792</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1060,6 +1080,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123333793</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1157,6 +1182,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123333794</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1259,6 +1289,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123333779</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1361,6 +1396,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123333781</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1463,6 +1503,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123333782</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1565,6 +1610,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123333783</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1667,6 +1717,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123333784</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1769,6 +1824,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123333785</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1871,6 +1931,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123333786</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -1973,6 +2038,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123333787</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2075,6 +2145,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123333788</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2177,6 +2252,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123333789</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2287,8 +2367,31 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123333795</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>